--- a/DATA KOPERASI.xlsx
+++ b/DATA KOPERASI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07F67A4-2B44-4E04-AEA5-102044F49E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E4DA4F-4E1C-46F1-824F-ECC82B461619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="723" activeTab="3" xr2:uid="{F970B87B-20DA-4A5C-AAEA-A159F2A492B1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="723" activeTab="1" xr2:uid="{F970B87B-20DA-4A5C-AAEA-A159F2A492B1}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet 1" sheetId="37" r:id="rId1"/>
@@ -5722,7 +5722,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5770,7 +5770,6 @@
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="46">
@@ -11669,7 +11668,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="25" t="s">
         <v>249</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -11680,7 +11679,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="25" t="s">
         <v>240</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -11691,7 +11690,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="25" t="s">
         <v>267</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -11702,7 +11701,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>765</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -11713,7 +11712,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="25" t="s">
         <v>601</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -11724,7 +11723,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>798</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -11735,7 +11734,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="25" t="s">
         <v>170</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -11746,7 +11745,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="25" t="s">
         <v>406</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -11757,7 +11756,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="25" t="s">
         <v>253</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -11768,7 +11767,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="25" t="s">
         <v>541</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -11779,7 +11778,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="25" t="s">
         <v>621</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -11790,7 +11789,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="25" t="s">
         <v>294</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -11801,7 +11800,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="25" t="s">
         <v>619</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -11812,7 +11811,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="25" t="s">
         <v>737</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -11823,7 +11822,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="25" t="s">
         <v>210</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -11834,7 +11833,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>404</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -11845,7 +11844,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="25" t="s">
         <v>743</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -11856,7 +11855,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="25" t="s">
         <v>203</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -11867,7 +11866,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="25" t="s">
         <v>697</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -11878,7 +11877,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="25" t="s">
         <v>463</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -11889,7 +11888,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="25" t="s">
         <v>512</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -11900,7 +11899,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="26" t="s">
+      <c r="A23" s="25" t="s">
         <v>460</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -11911,7 +11910,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="25" t="s">
         <v>397</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -11922,7 +11921,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="25" t="s">
         <v>296</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -11933,7 +11932,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="25" t="s">
         <v>581</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -11944,7 +11943,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="25" t="s">
         <v>200</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -11955,7 +11954,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="25" t="s">
         <v>520</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -11966,7 +11965,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="25" t="s">
         <v>702</v>
       </c>
       <c r="B29" s="6" t="s">
@@ -11977,7 +11976,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="25" t="s">
         <v>593</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -11988,7 +11987,7 @@
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="25" t="s">
         <v>136</v>
       </c>
       <c r="B31" s="6" t="s">
@@ -11999,7 +11998,7 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="25" t="s">
         <v>629</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -12010,7 +12009,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="25" t="s">
         <v>599</v>
       </c>
       <c r="B33" s="6" t="s">
@@ -12021,7 +12020,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="25" t="s">
         <v>350</v>
       </c>
       <c r="B34" s="6" t="s">
@@ -12032,7 +12031,7 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="25" t="s">
         <v>91</v>
       </c>
       <c r="B35" s="6" t="s">
@@ -12043,7 +12042,7 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="26" t="s">
+      <c r="A36" s="25" t="s">
         <v>586</v>
       </c>
       <c r="B36" s="6" t="s">
@@ -12054,7 +12053,7 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="26" t="s">
+      <c r="A37" s="25" t="s">
         <v>482</v>
       </c>
       <c r="B37" s="6" t="s">
@@ -12065,7 +12064,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="26" t="s">
+      <c r="A38" s="25" t="s">
         <v>69</v>
       </c>
       <c r="B38" s="6" t="s">
@@ -12076,7 +12075,7 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="26" t="s">
+      <c r="A39" s="25" t="s">
         <v>557</v>
       </c>
       <c r="B39" s="6" t="s">
@@ -12087,7 +12086,7 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="26" t="s">
+      <c r="A40" s="25" t="s">
         <v>55</v>
       </c>
       <c r="B40" s="6" t="s">
@@ -12098,7 +12097,7 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="26" t="s">
+      <c r="A41" s="25" t="s">
         <v>527</v>
       </c>
       <c r="B41" s="6" t="s">
@@ -12109,7 +12108,7 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="26" t="s">
+      <c r="A42" s="25" t="s">
         <v>562</v>
       </c>
       <c r="B42" s="6" t="s">
@@ -12120,7 +12119,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="26" t="s">
+      <c r="A43" s="25" t="s">
         <v>779</v>
       </c>
       <c r="B43" s="6" t="s">
@@ -12131,7 +12130,7 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="26" t="s">
+      <c r="A44" s="25" t="s">
         <v>212</v>
       </c>
       <c r="B44" s="6" t="s">
@@ -12142,7 +12141,7 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="26" t="s">
+      <c r="A45" s="25" t="s">
         <v>664</v>
       </c>
       <c r="B45" s="6" t="s">
@@ -12153,7 +12152,7 @@
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="26" t="s">
+      <c r="A46" s="25" t="s">
         <v>382</v>
       </c>
       <c r="B46" s="6" t="s">
@@ -12164,7 +12163,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="26" t="s">
+      <c r="A47" s="25" t="s">
         <v>457</v>
       </c>
       <c r="B47" s="6" t="s">
@@ -12175,7 +12174,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="26" t="s">
+      <c r="A48" s="25" t="s">
         <v>1223</v>
       </c>
       <c r="B48" s="6" t="s">
@@ -12186,7 +12185,7 @@
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="26" t="s">
+      <c r="A49" s="25" t="s">
         <v>653</v>
       </c>
       <c r="B49" s="6" t="s">
@@ -12197,7 +12196,7 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="26" t="s">
+      <c r="A50" s="25" t="s">
         <v>770</v>
       </c>
       <c r="B50" s="6" t="s">
@@ -12208,7 +12207,7 @@
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="26" t="s">
+      <c r="A51" s="25" t="s">
         <v>28</v>
       </c>
       <c r="B51" s="6" t="s">
@@ -12219,7 +12218,7 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="26" t="s">
+      <c r="A52" s="25" t="s">
         <v>1115</v>
       </c>
       <c r="B52" s="6" t="s">
@@ -12230,7 +12229,7 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="26" t="s">
+      <c r="A53" s="25" t="s">
         <v>659</v>
       </c>
       <c r="B53" s="6" t="s">
@@ -12241,7 +12240,7 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="26" t="s">
+      <c r="A54" s="25" t="s">
         <v>800</v>
       </c>
       <c r="B54" s="6" t="s">
@@ -12252,7 +12251,7 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="26" t="s">
+      <c r="A55" s="25" t="s">
         <v>311</v>
       </c>
       <c r="B55" s="6" t="s">
@@ -12263,7 +12262,7 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="26" t="s">
+      <c r="A56" s="25" t="s">
         <v>1224</v>
       </c>
       <c r="B56" s="6" t="s">
@@ -12274,7 +12273,7 @@
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="26" t="s">
+      <c r="A57" s="25" t="s">
         <v>388</v>
       </c>
       <c r="B57" s="6" t="s">
@@ -12285,7 +12284,7 @@
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="26" t="s">
+      <c r="A58" s="25" t="s">
         <v>222</v>
       </c>
       <c r="B58" s="6" t="s">
@@ -12296,7 +12295,7 @@
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="26" t="s">
+      <c r="A59" s="25" t="s">
         <v>385</v>
       </c>
       <c r="B59" s="6" t="s">
@@ -12307,7 +12306,7 @@
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="26" t="s">
+      <c r="A60" s="25" t="s">
         <v>687</v>
       </c>
       <c r="B60" s="6" t="s">
@@ -12318,7 +12317,7 @@
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="26" t="s">
+      <c r="A61" s="25" t="s">
         <v>786</v>
       </c>
       <c r="B61" s="6" t="s">
@@ -12329,7 +12328,7 @@
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="26" t="s">
+      <c r="A62" s="25" t="s">
         <v>799</v>
       </c>
       <c r="B62" s="6" t="s">
@@ -12340,7 +12339,7 @@
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="26" t="s">
+      <c r="A63" s="25" t="s">
         <v>194</v>
       </c>
       <c r="B63" s="6" t="s">
@@ -12351,7 +12350,7 @@
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="26" t="s">
+      <c r="A64" s="25" t="s">
         <v>46</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -12362,7 +12361,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65" s="26" t="s">
+      <c r="A65" s="25" t="s">
         <v>596</v>
       </c>
       <c r="B65" s="6" t="s">
@@ -12373,7 +12372,7 @@
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" s="26" t="s">
+      <c r="A66" s="25" t="s">
         <v>138</v>
       </c>
       <c r="B66" s="6" t="s">
@@ -12384,7 +12383,7 @@
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" s="26" t="s">
+      <c r="A67" s="25" t="s">
         <v>493</v>
       </c>
       <c r="B67" s="6" t="s">
@@ -12395,7 +12394,7 @@
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" s="26" t="s">
+      <c r="A68" s="25" t="s">
         <v>256</v>
       </c>
       <c r="B68" s="6" t="s">
@@ -12406,7 +12405,7 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" s="26" t="s">
+      <c r="A69" s="25" t="s">
         <v>808</v>
       </c>
       <c r="B69" s="6" t="s">
@@ -12417,7 +12416,7 @@
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" s="26" t="s">
+      <c r="A70" s="25" t="s">
         <v>590</v>
       </c>
       <c r="B70" s="6" t="s">
@@ -12428,7 +12427,7 @@
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71" s="26" t="s">
+      <c r="A71" s="25" t="s">
         <v>1116</v>
       </c>
       <c r="B71" s="6" t="s">
@@ -12439,7 +12438,7 @@
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72" s="26" t="s">
+      <c r="A72" s="25" t="s">
         <v>723</v>
       </c>
       <c r="B72" s="6" t="s">
@@ -12450,7 +12449,7 @@
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A73" s="26" t="s">
+      <c r="A73" s="25" t="s">
         <v>361</v>
       </c>
       <c r="B73" s="6" t="s">
@@ -12461,7 +12460,7 @@
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74" s="26" t="s">
+      <c r="A74" s="25" t="s">
         <v>167</v>
       </c>
       <c r="B74" s="6" t="s">
@@ -12472,7 +12471,7 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75" s="26" t="s">
+      <c r="A75" s="25" t="s">
         <v>126</v>
       </c>
       <c r="B75" s="6" t="s">
@@ -12483,7 +12482,7 @@
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76" s="26" t="s">
+      <c r="A76" s="25" t="s">
         <v>332</v>
       </c>
       <c r="B76" s="6" t="s">
@@ -12494,7 +12493,7 @@
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77" s="26" t="s">
+      <c r="A77" s="25" t="s">
         <v>120</v>
       </c>
       <c r="B77" s="6" t="s">
@@ -12505,7 +12504,7 @@
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78" s="26" t="s">
+      <c r="A78" s="25" t="s">
         <v>507</v>
       </c>
       <c r="B78" s="6" t="s">
@@ -12516,7 +12515,7 @@
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79" s="26" t="s">
+      <c r="A79" s="25" t="s">
         <v>1117</v>
       </c>
       <c r="B79" s="6" t="s">
@@ -12527,7 +12526,7 @@
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80" s="26" t="s">
+      <c r="A80" s="25" t="s">
         <v>1118</v>
       </c>
       <c r="B80" s="6" t="s">
@@ -12538,7 +12537,7 @@
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A81" s="26" t="s">
+      <c r="A81" s="25" t="s">
         <v>94</v>
       </c>
       <c r="B81" s="6" t="s">
@@ -12549,7 +12548,7 @@
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A82" s="26" t="s">
+      <c r="A82" s="25" t="s">
         <v>376</v>
       </c>
       <c r="B82" s="6" t="s">
@@ -12560,7 +12559,7 @@
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A83" s="26" t="s">
+      <c r="A83" s="25" t="s">
         <v>777</v>
       </c>
       <c r="B83" s="6" t="s">
@@ -12571,7 +12570,7 @@
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A84" s="26" t="s">
+      <c r="A84" s="25" t="s">
         <v>258</v>
       </c>
       <c r="B84" s="6" t="s">
@@ -12582,7 +12581,7 @@
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A85" s="26" t="s">
+      <c r="A85" s="25" t="s">
         <v>129</v>
       </c>
       <c r="B85" s="6" t="s">
@@ -12593,7 +12592,7 @@
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A86" s="26" t="s">
+      <c r="A86" s="25" t="s">
         <v>730</v>
       </c>
       <c r="B86" s="6" t="s">
@@ -12604,7 +12603,7 @@
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A87" s="26" t="s">
+      <c r="A87" s="25" t="s">
         <v>386</v>
       </c>
       <c r="B87" s="6" t="s">
@@ -12615,7 +12614,7 @@
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A88" s="26" t="s">
+      <c r="A88" s="25" t="s">
         <v>39</v>
       </c>
       <c r="B88" s="6" t="s">
@@ -12626,7 +12625,7 @@
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A89" s="26" t="s">
+      <c r="A89" s="25" t="s">
         <v>73</v>
       </c>
       <c r="B89" s="6" t="s">
@@ -12637,7 +12636,7 @@
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A90" s="26" t="s">
+      <c r="A90" s="25" t="s">
         <v>180</v>
       </c>
       <c r="B90" s="6" t="s">
@@ -12648,7 +12647,7 @@
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A91" s="26" t="s">
+      <c r="A91" s="25" t="s">
         <v>115</v>
       </c>
       <c r="B91" s="6" t="s">
@@ -12659,7 +12658,7 @@
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A92" s="26" t="s">
+      <c r="A92" s="25" t="s">
         <v>534</v>
       </c>
       <c r="B92" s="6" t="s">
@@ -12670,7 +12669,7 @@
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A93" s="26" t="s">
+      <c r="A93" s="25" t="s">
         <v>652</v>
       </c>
       <c r="B93" s="6" t="s">
@@ -12681,7 +12680,7 @@
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A94" s="26" t="s">
+      <c r="A94" s="25" t="s">
         <v>320</v>
       </c>
       <c r="B94" s="6" t="s">
@@ -12692,7 +12691,7 @@
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A95" s="26" t="s">
+      <c r="A95" s="25" t="s">
         <v>322</v>
       </c>
       <c r="B95" s="6" t="s">
@@ -12703,7 +12702,7 @@
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A96" s="26" t="s">
+      <c r="A96" s="25" t="s">
         <v>591</v>
       </c>
       <c r="B96" s="6" t="s">
@@ -12714,7 +12713,7 @@
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A97" s="26" t="s">
+      <c r="A97" s="25" t="s">
         <v>726</v>
       </c>
       <c r="B97" s="6" t="s">
@@ -12725,7 +12724,7 @@
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A98" s="26" t="s">
+      <c r="A98" s="25" t="s">
         <v>329</v>
       </c>
       <c r="B98" s="6" t="s">
@@ -12736,7 +12735,7 @@
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A99" s="26" t="s">
+      <c r="A99" s="25" t="s">
         <v>1119</v>
       </c>
       <c r="B99" s="6" t="s">
@@ -12747,7 +12746,7 @@
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100" s="26" t="s">
+      <c r="A100" s="25" t="s">
         <v>1120</v>
       </c>
       <c r="B100" s="6" t="s">
@@ -12758,7 +12757,7 @@
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A101" s="26" t="s">
+      <c r="A101" s="25" t="s">
         <v>316</v>
       </c>
       <c r="B101" s="6" t="s">
@@ -12769,7 +12768,7 @@
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A102" s="26" t="s">
+      <c r="A102" s="25" t="s">
         <v>1121</v>
       </c>
       <c r="B102" s="6" t="s">
@@ -12780,7 +12779,7 @@
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A103" s="26" t="s">
+      <c r="A103" s="25" t="s">
         <v>408</v>
       </c>
       <c r="B103" s="6" t="s">
@@ -12791,7 +12790,7 @@
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A104" s="26" t="s">
+      <c r="A104" s="25" t="s">
         <v>616</v>
       </c>
       <c r="B104" s="6" t="s">
@@ -12802,7 +12801,7 @@
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A105" s="26" t="s">
+      <c r="A105" s="25" t="s">
         <v>250</v>
       </c>
       <c r="B105" s="6" t="s">
@@ -12813,7 +12812,7 @@
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A106" s="26" t="s">
+      <c r="A106" s="25" t="s">
         <v>715</v>
       </c>
       <c r="B106" s="6" t="s">
@@ -12824,7 +12823,7 @@
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A107" s="26" t="s">
+      <c r="A107" s="25" t="s">
         <v>1226</v>
       </c>
       <c r="B107" s="6" t="s">
@@ -12835,7 +12834,7 @@
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A108" s="26" t="s">
+      <c r="A108" s="25" t="s">
         <v>492</v>
       </c>
       <c r="B108" s="6" t="s">
@@ -12846,7 +12845,7 @@
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A109" s="26" t="s">
+      <c r="A109" s="25" t="s">
         <v>35</v>
       </c>
       <c r="B109" s="6" t="s">
@@ -12857,7 +12856,7 @@
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A110" s="26" t="s">
+      <c r="A110" s="25" t="s">
         <v>784</v>
       </c>
       <c r="B110" s="6" t="s">
@@ -12868,7 +12867,7 @@
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A111" s="26" t="s">
+      <c r="A111" s="25" t="s">
         <v>804</v>
       </c>
       <c r="B111" s="6" t="s">
@@ -12879,7 +12878,7 @@
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A112" s="26" t="s">
+      <c r="A112" s="25" t="s">
         <v>1122</v>
       </c>
       <c r="B112" s="6" t="s">
@@ -12890,7 +12889,7 @@
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A113" s="26" t="s">
+      <c r="A113" s="25" t="s">
         <v>356</v>
       </c>
       <c r="B113" s="6" t="s">
@@ -12901,7 +12900,7 @@
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A114" s="26" t="s">
+      <c r="A114" s="25" t="s">
         <v>21</v>
       </c>
       <c r="B114" s="6" t="s">
@@ -12912,7 +12911,7 @@
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A115" s="26" t="s">
+      <c r="A115" s="25" t="s">
         <v>1123</v>
       </c>
       <c r="B115" s="6" t="s">
@@ -12923,7 +12922,7 @@
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A116" s="26" t="s">
+      <c r="A116" s="25" t="s">
         <v>123</v>
       </c>
       <c r="B116" s="6" t="s">
@@ -12934,7 +12933,7 @@
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A117" s="26" t="s">
+      <c r="A117" s="25" t="s">
         <v>1124</v>
       </c>
       <c r="B117" s="6" t="s">
@@ -12945,7 +12944,7 @@
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A118" s="26" t="s">
+      <c r="A118" s="25" t="s">
         <v>230</v>
       </c>
       <c r="B118" s="6" t="s">
@@ -12956,7 +12955,7 @@
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A119" s="26" t="s">
+      <c r="A119" s="25" t="s">
         <v>661</v>
       </c>
       <c r="B119" s="6" t="s">
@@ -12967,7 +12966,7 @@
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A120" s="26" t="s">
+      <c r="A120" s="25" t="s">
         <v>187</v>
       </c>
       <c r="B120" s="6" t="s">
@@ -12978,7 +12977,7 @@
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A121" s="26" t="s">
+      <c r="A121" s="25" t="s">
         <v>716</v>
       </c>
       <c r="B121" s="6" t="s">
@@ -12989,7 +12988,7 @@
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A122" s="26" t="s">
+      <c r="A122" s="25" t="s">
         <v>513</v>
       </c>
       <c r="B122" s="6" t="s">
@@ -13000,7 +12999,7 @@
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A123" s="26" t="s">
+      <c r="A123" s="25" t="s">
         <v>646</v>
       </c>
       <c r="B123" s="6" t="s">
@@ -13011,7 +13010,7 @@
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A124" s="26" t="s">
+      <c r="A124" s="25" t="s">
         <v>325</v>
       </c>
       <c r="B124" s="6" t="s">
@@ -13022,7 +13021,7 @@
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A125" s="26" t="s">
+      <c r="A125" s="25" t="s">
         <v>269</v>
       </c>
       <c r="B125" s="6" t="s">
@@ -13033,7 +13032,7 @@
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A126" s="26" t="s">
+      <c r="A126" s="25" t="s">
         <v>547</v>
       </c>
       <c r="B126" s="6" t="s">
@@ -13044,7 +13043,7 @@
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A127" s="26" t="s">
+      <c r="A127" s="25" t="s">
         <v>143</v>
       </c>
       <c r="B127" s="6" t="s">
@@ -13055,7 +13054,7 @@
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A128" s="26" t="s">
+      <c r="A128" s="25" t="s">
         <v>606</v>
       </c>
       <c r="B128" s="6" t="s">
@@ -13066,7 +13065,7 @@
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A129" s="26" t="s">
+      <c r="A129" s="25" t="s">
         <v>1125</v>
       </c>
       <c r="B129" s="6" t="s">
@@ -13077,7 +13076,7 @@
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A130" s="26" t="s">
+      <c r="A130" s="25" t="s">
         <v>611</v>
       </c>
       <c r="B130" s="6" t="s">
@@ -13088,7 +13087,7 @@
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A131" s="26" t="s">
+      <c r="A131" s="25" t="s">
         <v>756</v>
       </c>
       <c r="B131" s="6" t="s">
@@ -13099,7 +13098,7 @@
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A132" s="26" t="s">
+      <c r="A132" s="25" t="s">
         <v>607</v>
       </c>
       <c r="B132" s="6" t="s">
@@ -13110,7 +13109,7 @@
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A133" s="26" t="s">
+      <c r="A133" s="25" t="s">
         <v>88</v>
       </c>
       <c r="B133" s="6" t="s">
@@ -13121,7 +13120,7 @@
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A134" s="26" t="s">
+      <c r="A134" s="25" t="s">
         <v>1227</v>
       </c>
       <c r="B134" s="6" t="s">
@@ -13132,7 +13131,7 @@
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A135" s="26" t="s">
+      <c r="A135" s="25" t="s">
         <v>485</v>
       </c>
       <c r="B135" s="6" t="s">
@@ -13143,7 +13142,7 @@
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A136" s="26" t="s">
+      <c r="A136" s="25" t="s">
         <v>403</v>
       </c>
       <c r="B136" s="6" t="s">
@@ -13154,7 +13153,7 @@
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A137" s="26" t="s">
+      <c r="A137" s="25" t="s">
         <v>809</v>
       </c>
       <c r="B137" s="6" t="s">
@@ -13165,7 +13164,7 @@
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A138" s="26" t="s">
+      <c r="A138" s="25" t="s">
         <v>228</v>
       </c>
       <c r="B138" s="6" t="s">
@@ -13176,7 +13175,7 @@
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A139" s="26" t="s">
+      <c r="A139" s="25" t="s">
         <v>287</v>
       </c>
       <c r="B139" s="6" t="s">
@@ -13187,7 +13186,7 @@
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A140" s="26" t="s">
+      <c r="A140" s="25" t="s">
         <v>724</v>
       </c>
       <c r="B140" s="6" t="s">
@@ -13198,7 +13197,7 @@
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A141" s="26" t="s">
+      <c r="A141" s="25" t="s">
         <v>497</v>
       </c>
       <c r="B141" s="6" t="s">
@@ -13209,7 +13208,7 @@
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A142" s="26" t="s">
+      <c r="A142" s="25" t="s">
         <v>683</v>
       </c>
       <c r="B142" s="6" t="s">
@@ -13220,7 +13219,7 @@
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A143" s="26" t="s">
+      <c r="A143" s="25" t="s">
         <v>197</v>
       </c>
       <c r="B143" s="6" t="s">
@@ -13231,7 +13230,7 @@
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A144" s="26" t="s">
+      <c r="A144" s="25" t="s">
         <v>1126</v>
       </c>
       <c r="B144" s="6" t="s">
@@ -13242,7 +13241,7 @@
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A145" s="26" t="s">
+      <c r="A145" s="25" t="s">
         <v>218</v>
       </c>
       <c r="B145" s="6" t="s">
@@ -13253,7 +13252,7 @@
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A146" s="26" t="s">
+      <c r="A146" s="25" t="s">
         <v>113</v>
       </c>
       <c r="B146" s="6" t="s">
@@ -13264,7 +13263,7 @@
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A147" s="26" t="s">
+      <c r="A147" s="25" t="s">
         <v>391</v>
       </c>
       <c r="B147" s="6" t="s">
@@ -13275,7 +13274,7 @@
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A148" s="26" t="s">
+      <c r="A148" s="25" t="s">
         <v>1127</v>
       </c>
       <c r="B148" s="6" t="s">
@@ -13286,7 +13285,7 @@
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A149" s="26" t="s">
+      <c r="A149" s="25" t="s">
         <v>33</v>
       </c>
       <c r="B149" s="6" t="s">
@@ -13297,7 +13296,7 @@
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A150" s="26" t="s">
+      <c r="A150" s="25" t="s">
         <v>684</v>
       </c>
       <c r="B150" s="6" t="s">
@@ -13308,7 +13307,7 @@
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A151" s="26" t="s">
+      <c r="A151" s="25" t="s">
         <v>208</v>
       </c>
       <c r="B151" s="6" t="s">
@@ -13319,7 +13318,7 @@
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A152" s="26" t="s">
+      <c r="A152" s="25" t="s">
         <v>1228</v>
       </c>
       <c r="B152" s="6" t="s">
@@ -13330,7 +13329,7 @@
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A153" s="26" t="s">
+      <c r="A153" s="25" t="s">
         <v>528</v>
       </c>
       <c r="B153" s="6" t="s">
@@ -13341,7 +13340,7 @@
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A154" s="26" t="s">
+      <c r="A154" s="25" t="s">
         <v>773</v>
       </c>
       <c r="B154" s="6" t="s">
@@ -13352,7 +13351,7 @@
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A155" s="26" t="s">
+      <c r="A155" s="25" t="s">
         <v>1128</v>
       </c>
       <c r="B155" s="6" t="s">
@@ -13363,7 +13362,7 @@
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A156" s="26" t="s">
+      <c r="A156" s="25" t="s">
         <v>455</v>
       </c>
       <c r="B156" s="6" t="s">
@@ -13374,7 +13373,7 @@
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A157" s="26" t="s">
+      <c r="A157" s="25" t="s">
         <v>108</v>
       </c>
       <c r="B157" s="6" t="s">
@@ -13385,7 +13384,7 @@
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A158" s="26" t="s">
+      <c r="A158" s="25" t="s">
         <v>206</v>
       </c>
       <c r="B158" s="6" t="s">
@@ -13396,7 +13395,7 @@
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A159" s="26" t="s">
+      <c r="A159" s="25" t="s">
         <v>801</v>
       </c>
       <c r="B159" s="6" t="s">
@@ -13407,7 +13406,7 @@
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A160" s="26" t="s">
+      <c r="A160" s="25" t="s">
         <v>1129</v>
       </c>
       <c r="B160" s="6" t="s">
@@ -13418,7 +13417,7 @@
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A161" s="26" t="s">
+      <c r="A161" s="25" t="s">
         <v>79</v>
       </c>
       <c r="B161" s="6" t="s">
@@ -13429,7 +13428,7 @@
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A162" s="26" t="s">
+      <c r="A162" s="25" t="s">
         <v>585</v>
       </c>
       <c r="B162" s="6" t="s">
@@ -13440,7 +13439,7 @@
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A163" s="26" t="s">
+      <c r="A163" s="25" t="s">
         <v>755</v>
       </c>
       <c r="B163" s="6" t="s">
@@ -13451,7 +13450,7 @@
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A164" s="26" t="s">
+      <c r="A164" s="25" t="s">
         <v>517</v>
       </c>
       <c r="B164" s="6" t="s">
@@ -13462,7 +13461,7 @@
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A165" s="26" t="s">
+      <c r="A165" s="25" t="s">
         <v>213</v>
       </c>
       <c r="B165" s="6" t="s">
@@ -13473,7 +13472,7 @@
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A166" s="26" t="s">
+      <c r="A166" s="25" t="s">
         <v>795</v>
       </c>
       <c r="B166" s="6" t="s">
@@ -13484,7 +13483,7 @@
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A167" s="26" t="s">
+      <c r="A167" s="25" t="s">
         <v>279</v>
       </c>
       <c r="B167" s="6" t="s">
@@ -13495,7 +13494,7 @@
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A168" s="26" t="s">
+      <c r="A168" s="25" t="s">
         <v>84</v>
       </c>
       <c r="B168" s="6" t="s">
@@ -13506,7 +13505,7 @@
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A169" s="26" t="s">
+      <c r="A169" s="25" t="s">
         <v>515</v>
       </c>
       <c r="B169" s="6" t="s">
@@ -13517,7 +13516,7 @@
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A170" s="26" t="s">
+      <c r="A170" s="25" t="s">
         <v>1130</v>
       </c>
       <c r="B170" s="6" t="s">
@@ -13528,7 +13527,7 @@
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A171" s="26" t="s">
+      <c r="A171" s="25" t="s">
         <v>471</v>
       </c>
       <c r="B171" s="6" t="s">
@@ -13539,7 +13538,7 @@
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A172" s="26" t="s">
+      <c r="A172" s="25" t="s">
         <v>80</v>
       </c>
       <c r="B172" s="6" t="s">
@@ -13550,7 +13549,7 @@
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A173" s="26" t="s">
+      <c r="A173" s="25" t="s">
         <v>141</v>
       </c>
       <c r="B173" s="6" t="s">
@@ -13561,7 +13560,7 @@
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A174" s="26" t="s">
+      <c r="A174" s="25" t="s">
         <v>328</v>
       </c>
       <c r="B174" s="6" t="s">
@@ -13572,7 +13571,7 @@
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A175" s="26" t="s">
+      <c r="A175" s="25" t="s">
         <v>504</v>
       </c>
       <c r="B175" s="6" t="s">
@@ -13583,7 +13582,7 @@
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A176" s="26" t="s">
+      <c r="A176" s="25" t="s">
         <v>686</v>
       </c>
       <c r="B176" s="6" t="s">
@@ -13594,7 +13593,7 @@
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A177" s="26" t="s">
+      <c r="A177" s="25" t="s">
         <v>19</v>
       </c>
       <c r="B177" s="6" t="s">
@@ -13605,7 +13604,7 @@
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A178" s="26" t="s">
+      <c r="A178" s="25" t="s">
         <v>768</v>
       </c>
       <c r="B178" s="6" t="s">
@@ -13616,7 +13615,7 @@
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A179" s="26" t="s">
+      <c r="A179" s="25" t="s">
         <v>660</v>
       </c>
       <c r="B179" s="6" t="s">
@@ -13627,7 +13626,7 @@
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A180" s="26" t="s">
+      <c r="A180" s="25" t="s">
         <v>152</v>
       </c>
       <c r="B180" s="6" t="s">
@@ -13638,7 +13637,7 @@
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A181" s="26" t="s">
+      <c r="A181" s="25" t="s">
         <v>634</v>
       </c>
       <c r="B181" s="6" t="s">
@@ -13649,7 +13648,7 @@
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A182" s="26" t="s">
+      <c r="A182" s="25" t="s">
         <v>1131</v>
       </c>
       <c r="B182" s="6" t="s">
@@ -13660,7 +13659,7 @@
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A183" s="26" t="s">
+      <c r="A183" s="25" t="s">
         <v>292</v>
       </c>
       <c r="B183" s="6" t="s">
@@ -13671,7 +13670,7 @@
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A184" s="26" t="s">
+      <c r="A184" s="25" t="s">
         <v>490</v>
       </c>
       <c r="B184" s="6" t="s">
@@ -13682,7 +13681,7 @@
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A185" s="26" t="s">
+      <c r="A185" s="25" t="s">
         <v>633</v>
       </c>
       <c r="B185" s="6" t="s">
@@ -13693,7 +13692,7 @@
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A186" s="26" t="s">
+      <c r="A186" s="25" t="s">
         <v>26</v>
       </c>
       <c r="B186" s="6" t="s">
@@ -13704,7 +13703,7 @@
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A187" s="26" t="s">
+      <c r="A187" s="25" t="s">
         <v>486</v>
       </c>
       <c r="B187" s="6" t="s">
@@ -13715,7 +13714,7 @@
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A188" s="26" t="s">
+      <c r="A188" s="25" t="s">
         <v>772</v>
       </c>
       <c r="B188" s="6" t="s">
@@ -13726,7 +13725,7 @@
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A189" s="26" t="s">
+      <c r="A189" s="25" t="s">
         <v>41</v>
       </c>
       <c r="B189" s="6" t="s">
@@ -13737,7 +13736,7 @@
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A190" s="26" t="s">
+      <c r="A190" s="25" t="s">
         <v>313</v>
       </c>
       <c r="B190" s="6" t="s">
@@ -13748,7 +13747,7 @@
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A191" s="26" t="s">
+      <c r="A191" s="25" t="s">
         <v>315</v>
       </c>
       <c r="B191" s="6" t="s">
@@ -13759,7 +13758,7 @@
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A192" s="26" t="s">
+      <c r="A192" s="25" t="s">
         <v>43</v>
       </c>
       <c r="B192" s="6" t="s">
@@ -13770,7 +13769,7 @@
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A193" s="26" t="s">
+      <c r="A193" s="25" t="s">
         <v>121</v>
       </c>
       <c r="B193" s="6" t="s">
@@ -13781,7 +13780,7 @@
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A194" s="26" t="s">
+      <c r="A194" s="25" t="s">
         <v>255</v>
       </c>
       <c r="B194" s="6" t="s">
@@ -13792,7 +13791,7 @@
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A195" s="26" t="s">
+      <c r="A195" s="25" t="s">
         <v>456</v>
       </c>
       <c r="B195" s="6" t="s">
@@ -13803,7 +13802,7 @@
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A196" s="26" t="s">
+      <c r="A196" s="25" t="s">
         <v>4</v>
       </c>
       <c r="B196" s="6" t="s">
@@ -13814,7 +13813,7 @@
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A197" s="26" t="s">
+      <c r="A197" s="25" t="s">
         <v>732</v>
       </c>
       <c r="B197" s="6" t="s">
@@ -13825,7 +13824,7 @@
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A198" s="26" t="s">
+      <c r="A198" s="25" t="s">
         <v>1133</v>
       </c>
       <c r="B198" s="6" t="s">
@@ -13836,7 +13835,7 @@
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A199" s="26" t="s">
+      <c r="A199" s="25" t="s">
         <v>480</v>
       </c>
       <c r="B199" s="6" t="s">
@@ -13847,7 +13846,7 @@
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A200" s="26" t="s">
+      <c r="A200" s="25" t="s">
         <v>714</v>
       </c>
       <c r="B200" s="6" t="s">
@@ -13858,7 +13857,7 @@
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A201" s="26" t="s">
+      <c r="A201" s="25" t="s">
         <v>729</v>
       </c>
       <c r="B201" s="6" t="s">
@@ -13869,7 +13868,7 @@
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A202" s="26" t="s">
+      <c r="A202" s="25" t="s">
         <v>789</v>
       </c>
       <c r="B202" s="6" t="s">
@@ -13880,7 +13879,7 @@
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A203" s="26" t="s">
+      <c r="A203" s="25" t="s">
         <v>533</v>
       </c>
       <c r="B203" s="6" t="s">
@@ -13891,7 +13890,7 @@
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A204" s="26" t="s">
+      <c r="A204" s="25" t="s">
         <v>224</v>
       </c>
       <c r="B204" s="6" t="s">
@@ -13902,7 +13901,7 @@
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A205" s="26" t="s">
+      <c r="A205" s="25" t="s">
         <v>614</v>
       </c>
       <c r="B205" s="6" t="s">
@@ -13913,7 +13912,7 @@
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A206" s="26" t="s">
+      <c r="A206" s="25" t="s">
         <v>319</v>
       </c>
       <c r="B206" s="6" t="s">
@@ -13924,7 +13923,7 @@
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A207" s="26" t="s">
+      <c r="A207" s="25" t="s">
         <v>100</v>
       </c>
       <c r="B207" s="6" t="s">
@@ -13935,7 +13934,7 @@
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A208" s="26" t="s">
+      <c r="A208" s="25" t="s">
         <v>1134</v>
       </c>
       <c r="B208" s="6" t="s">
@@ -13946,7 +13945,7 @@
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A209" s="26" t="s">
+      <c r="A209" s="25" t="s">
         <v>539</v>
       </c>
       <c r="B209" s="6" t="s">
@@ -13957,7 +13956,7 @@
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A210" s="26" t="s">
+      <c r="A210" s="25" t="s">
         <v>749</v>
       </c>
       <c r="B210" s="6" t="s">
@@ -13968,7 +13967,7 @@
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A211" s="26" t="s">
+      <c r="A211" s="25" t="s">
         <v>217</v>
       </c>
       <c r="B211" s="6" t="s">
@@ -13979,7 +13978,7 @@
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A212" s="26" t="s">
+      <c r="A212" s="25" t="s">
         <v>344</v>
       </c>
       <c r="B212" s="6" t="s">
@@ -13990,7 +13989,7 @@
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A213" s="26" t="s">
+      <c r="A213" s="25" t="s">
         <v>184</v>
       </c>
       <c r="B213" s="6" t="s">
@@ -14001,7 +14000,7 @@
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A214" s="26" t="s">
+      <c r="A214" s="25" t="s">
         <v>339</v>
       </c>
       <c r="B214" s="6" t="s">
@@ -14012,7 +14011,7 @@
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A215" s="26" t="s">
+      <c r="A215" s="25" t="s">
         <v>68</v>
       </c>
       <c r="B215" s="6" t="s">
@@ -14023,7 +14022,7 @@
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A216" s="26" t="s">
+      <c r="A216" s="25" t="s">
         <v>525</v>
       </c>
       <c r="B216" s="6" t="s">
@@ -14034,7 +14033,7 @@
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A217" s="26" t="s">
+      <c r="A217" s="25" t="s">
         <v>418</v>
       </c>
       <c r="B217" s="6" t="s">
@@ -14045,7 +14044,7 @@
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A218" s="26" t="s">
+      <c r="A218" s="25" t="s">
         <v>78</v>
       </c>
       <c r="B218" s="6" t="s">
@@ -14056,7 +14055,7 @@
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A219" s="26" t="s">
+      <c r="A219" s="25" t="s">
         <v>335</v>
       </c>
       <c r="B219" s="6" t="s">
@@ -14067,7 +14066,7 @@
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A220" s="26" t="s">
+      <c r="A220" s="25" t="s">
         <v>338</v>
       </c>
       <c r="B220" s="6" t="s">
@@ -14078,7 +14077,7 @@
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A221" s="26" t="s">
+      <c r="A221" s="25" t="s">
         <v>537</v>
       </c>
       <c r="B221" s="6" t="s">
@@ -14089,7 +14088,7 @@
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A222" s="26" t="s">
+      <c r="A222" s="25" t="s">
         <v>663</v>
       </c>
       <c r="B222" s="6" t="s">
@@ -14100,7 +14099,7 @@
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A223" s="26" t="s">
+      <c r="A223" s="25" t="s">
         <v>1135</v>
       </c>
       <c r="B223" s="6" t="s">
@@ -14111,7 +14110,7 @@
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A224" s="26" t="s">
+      <c r="A224" s="25" t="s">
         <v>159</v>
       </c>
       <c r="B224" s="6" t="s">
@@ -14122,7 +14121,7 @@
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A225" s="26" t="s">
+      <c r="A225" s="25" t="s">
         <v>1136</v>
       </c>
       <c r="B225" s="6" t="s">
@@ -14133,7 +14132,7 @@
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A226" s="26" t="s">
+      <c r="A226" s="25" t="s">
         <v>30</v>
       </c>
       <c r="B226" s="6" t="s">
@@ -14144,7 +14143,7 @@
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A227" s="26" t="s">
+      <c r="A227" s="25" t="s">
         <v>618</v>
       </c>
       <c r="B227" s="6" t="s">
@@ -14155,7 +14154,7 @@
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A228" s="26" t="s">
+      <c r="A228" s="25" t="s">
         <v>400</v>
       </c>
       <c r="B228" s="6" t="s">
@@ -14166,7 +14165,7 @@
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A229" s="26" t="s">
+      <c r="A229" s="25" t="s">
         <v>718</v>
       </c>
       <c r="B229" s="6" t="s">
@@ -14177,7 +14176,7 @@
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A230" s="26" t="s">
+      <c r="A230" s="25" t="s">
         <v>443</v>
       </c>
       <c r="B230" s="6" t="s">
@@ -14188,7 +14187,7 @@
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A231" s="26" t="s">
+      <c r="A231" s="25" t="s">
         <v>531</v>
       </c>
       <c r="B231" s="6" t="s">
@@ -14199,7 +14198,7 @@
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A232" s="26" t="s">
+      <c r="A232" s="25" t="s">
         <v>298</v>
       </c>
       <c r="B232" s="6" t="s">
@@ -14210,7 +14209,7 @@
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A233" s="26" t="s">
+      <c r="A233" s="25" t="s">
         <v>71</v>
       </c>
       <c r="B233" s="6" t="s">
@@ -14221,7 +14220,7 @@
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A234" s="26" t="s">
+      <c r="A234" s="25" t="s">
         <v>337</v>
       </c>
       <c r="B234" s="6" t="s">
@@ -14232,7 +14231,7 @@
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A235" s="26" t="s">
+      <c r="A235" s="25" t="s">
         <v>421</v>
       </c>
       <c r="B235" s="6" t="s">
@@ -14243,7 +14242,7 @@
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A236" s="26" t="s">
+      <c r="A236" s="25" t="s">
         <v>59</v>
       </c>
       <c r="B236" s="6" t="s">
@@ -14254,7 +14253,7 @@
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A237" s="26" t="s">
+      <c r="A237" s="25" t="s">
         <v>17</v>
       </c>
       <c r="B237" s="6" t="s">
@@ -14265,7 +14264,7 @@
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A238" s="26" t="s">
+      <c r="A238" s="25" t="s">
         <v>423</v>
       </c>
       <c r="B238" s="6" t="s">
@@ -14276,7 +14275,7 @@
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A239" s="26" t="s">
+      <c r="A239" s="25" t="s">
         <v>307</v>
       </c>
       <c r="B239" s="6" t="s">
@@ -14287,7 +14286,7 @@
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A240" s="26" t="s">
+      <c r="A240" s="25" t="s">
         <v>308</v>
       </c>
       <c r="B240" s="6" t="s">
@@ -14298,7 +14297,7 @@
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A241" s="26" t="s">
+      <c r="A241" s="25" t="s">
         <v>309</v>
       </c>
       <c r="B241" s="6" t="s">
@@ -14309,18 +14308,18 @@
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A242" s="26" t="s">
+      <c r="A242" s="25" t="s">
         <v>161</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>160</v>
       </c>
       <c r="C242" s="7">
-        <v>5095000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A243" s="26" t="s">
+      <c r="A243" s="25" t="s">
         <v>712</v>
       </c>
       <c r="B243" s="6" t="s">
@@ -14331,7 +14330,7 @@
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A244" s="26" t="s">
+      <c r="A244" s="25" t="s">
         <v>769</v>
       </c>
       <c r="B244" s="6" t="s">
@@ -14342,7 +14341,7 @@
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A245" s="26" t="s">
+      <c r="A245" s="25" t="s">
         <v>499</v>
       </c>
       <c r="B245" s="6" t="s">
@@ -14353,7 +14352,7 @@
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A246" s="26" t="s">
+      <c r="A246" s="25" t="s">
         <v>631</v>
       </c>
       <c r="B246" s="6" t="s">
@@ -14364,7 +14363,7 @@
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A247" s="26" t="s">
+      <c r="A247" s="25" t="s">
         <v>426</v>
       </c>
       <c r="B247" s="6" t="s">
@@ -14375,7 +14374,7 @@
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A248" s="26" t="s">
+      <c r="A248" s="25" t="s">
         <v>305</v>
       </c>
       <c r="B248" s="6" t="s">
@@ -14386,7 +14385,7 @@
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A249" s="26" t="s">
+      <c r="A249" s="25" t="s">
         <v>263</v>
       </c>
       <c r="B249" s="6" t="s">
@@ -14397,7 +14396,7 @@
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A250" s="26" t="s">
+      <c r="A250" s="25" t="s">
         <v>677</v>
       </c>
       <c r="B250" s="6" t="s">
@@ -14408,7 +14407,7 @@
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A251" s="26" t="s">
+      <c r="A251" s="25" t="s">
         <v>788</v>
       </c>
       <c r="B251" s="6" t="s">
@@ -14419,7 +14418,7 @@
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A252" s="26" t="s">
+      <c r="A252" s="25" t="s">
         <v>181</v>
       </c>
       <c r="B252" s="6" t="s">
@@ -14430,7 +14429,7 @@
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A253" s="26" t="s">
+      <c r="A253" s="25" t="s">
         <v>787</v>
       </c>
       <c r="B253" s="6" t="s">
@@ -14441,7 +14440,7 @@
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A254" s="26" t="s">
+      <c r="A254" s="25" t="s">
         <v>561</v>
       </c>
       <c r="B254" s="6" t="s">
@@ -14452,7 +14451,7 @@
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A255" s="26" t="s">
+      <c r="A255" s="25" t="s">
         <v>232</v>
       </c>
       <c r="B255" s="6" t="s">
@@ -14463,7 +14462,7 @@
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A256" s="26" t="s">
+      <c r="A256" s="25" t="s">
         <v>739</v>
       </c>
       <c r="B256" s="6" t="s">
@@ -14474,7 +14473,7 @@
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A257" s="26" t="s">
+      <c r="A257" s="25" t="s">
         <v>300</v>
       </c>
       <c r="B257" s="6" t="s">
@@ -14485,7 +14484,7 @@
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A258" s="26" t="s">
+      <c r="A258" s="25" t="s">
         <v>114</v>
       </c>
       <c r="B258" s="6" t="s">
@@ -14496,7 +14495,7 @@
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A259" s="26" t="s">
+      <c r="A259" s="25" t="s">
         <v>118</v>
       </c>
       <c r="B259" s="6" t="s">
@@ -14507,7 +14506,7 @@
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A260" s="26" t="s">
+      <c r="A260" s="25" t="s">
         <v>171</v>
       </c>
       <c r="B260" s="6" t="s">
@@ -14518,7 +14517,7 @@
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A261" s="26" t="s">
+      <c r="A261" s="25" t="s">
         <v>3</v>
       </c>
       <c r="B261" s="6" t="s">
@@ -14529,7 +14528,7 @@
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A262" s="26" t="s">
+      <c r="A262" s="25" t="s">
         <v>2</v>
       </c>
       <c r="B262" s="6" t="s">
@@ -14540,7 +14539,7 @@
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A263" s="26" t="s">
+      <c r="A263" s="25" t="s">
         <v>77</v>
       </c>
       <c r="B263" s="6" t="s">
@@ -14551,7 +14550,7 @@
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A264" s="26" t="s">
+      <c r="A264" s="25" t="s">
         <v>67</v>
       </c>
       <c r="B264" s="6" t="s">
@@ -14562,7 +14561,7 @@
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A265" s="26" t="s">
+      <c r="A265" s="25" t="s">
         <v>545</v>
       </c>
       <c r="B265" s="6" t="s">
@@ -14573,7 +14572,7 @@
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A266" s="26" t="s">
+      <c r="A266" s="25" t="s">
         <v>458</v>
       </c>
       <c r="B266" s="6" t="s">
@@ -14584,7 +14583,7 @@
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A267" s="26" t="s">
+      <c r="A267" s="25" t="s">
         <v>603</v>
       </c>
       <c r="B267" s="6" t="s">
@@ -14595,7 +14594,7 @@
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A268" s="26" t="s">
+      <c r="A268" s="25" t="s">
         <v>502</v>
       </c>
       <c r="B268" s="6" t="s">
@@ -14606,7 +14605,7 @@
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A269" s="26" t="s">
+      <c r="A269" s="25" t="s">
         <v>500</v>
       </c>
       <c r="B269" s="6" t="s">
@@ -14617,7 +14616,7 @@
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A270" s="26" t="s">
+      <c r="A270" s="25" t="s">
         <v>162</v>
       </c>
       <c r="B270" s="6" t="s">
@@ -14628,7 +14627,7 @@
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A271" s="26" t="s">
+      <c r="A271" s="25" t="s">
         <v>297</v>
       </c>
       <c r="B271" s="6" t="s">
@@ -14639,7 +14638,7 @@
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A272" s="26" t="s">
+      <c r="A272" s="25" t="s">
         <v>190</v>
       </c>
       <c r="B272" s="6" t="s">
@@ -14650,7 +14649,7 @@
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A273" s="26" t="s">
+      <c r="A273" s="25" t="s">
         <v>248</v>
       </c>
       <c r="B273" s="6" t="s">
@@ -14661,7 +14660,7 @@
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A274" s="26" t="s">
+      <c r="A274" s="25" t="s">
         <v>1141</v>
       </c>
       <c r="B274" s="6" t="s">
@@ -14672,7 +14671,7 @@
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A275" s="26" t="s">
+      <c r="A275" s="25" t="s">
         <v>140</v>
       </c>
       <c r="B275" s="6" t="s">
@@ -14683,7 +14682,7 @@
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A276" s="26" t="s">
+      <c r="A276" s="25" t="s">
         <v>142</v>
       </c>
       <c r="B276" s="6" t="s">
@@ -14694,7 +14693,7 @@
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A277" s="26" t="s">
+      <c r="A277" s="25" t="s">
         <v>283</v>
       </c>
       <c r="B277" s="6" t="s">
@@ -14705,7 +14704,7 @@
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A278" s="26" t="s">
+      <c r="A278" s="25" t="s">
         <v>612</v>
       </c>
       <c r="B278" s="6" t="s">
@@ -14716,7 +14715,7 @@
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A279" s="26" t="s">
+      <c r="A279" s="25" t="s">
         <v>722</v>
       </c>
       <c r="B279" s="6" t="s">
@@ -14727,7 +14726,7 @@
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A280" s="26" t="s">
+      <c r="A280" s="25" t="s">
         <v>351</v>
       </c>
       <c r="B280" s="6" t="s">
@@ -14738,7 +14737,7 @@
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A281" s="26" t="s">
+      <c r="A281" s="25" t="s">
         <v>245</v>
       </c>
       <c r="B281" s="6" t="s">
@@ -14749,7 +14748,7 @@
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A282" s="26" t="s">
+      <c r="A282" s="25" t="s">
         <v>752</v>
       </c>
       <c r="B282" s="6" t="s">
@@ -14760,7 +14759,7 @@
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A283" s="26" t="s">
+      <c r="A283" s="25" t="s">
         <v>179</v>
       </c>
       <c r="B283" s="6" t="s">
@@ -14771,7 +14770,7 @@
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A284" s="26" t="s">
+      <c r="A284" s="25" t="s">
         <v>568</v>
       </c>
       <c r="B284" s="6" t="s">
@@ -14782,7 +14781,7 @@
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A285" s="26" t="s">
+      <c r="A285" s="25" t="s">
         <v>105</v>
       </c>
       <c r="B285" s="6" t="s">
@@ -14793,7 +14792,7 @@
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A286" s="26" t="s">
+      <c r="A286" s="25" t="s">
         <v>759</v>
       </c>
       <c r="B286" s="6" t="s">
@@ -14804,7 +14803,7 @@
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A287" s="26" t="s">
+      <c r="A287" s="25" t="s">
         <v>761</v>
       </c>
       <c r="B287" s="6" t="s">
@@ -14815,7 +14814,7 @@
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A288" s="26" t="s">
+      <c r="A288" s="25" t="s">
         <v>815</v>
       </c>
       <c r="B288" s="6" t="s">
@@ -14826,7 +14825,7 @@
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A289" s="26" t="s">
+      <c r="A289" s="25" t="s">
         <v>816</v>
       </c>
       <c r="B289" s="6" t="s">
@@ -14837,7 +14836,7 @@
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A290" s="26" t="s">
+      <c r="A290" s="25" t="s">
         <v>817</v>
       </c>
       <c r="B290" s="6" t="s">
@@ -14848,7 +14847,7 @@
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A291" s="26" t="s">
+      <c r="A291" s="25" t="s">
         <v>818</v>
       </c>
       <c r="B291" s="6" t="s">
@@ -14859,7 +14858,7 @@
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A292" s="26" t="s">
+      <c r="A292" s="25" t="s">
         <v>820</v>
       </c>
       <c r="B292" s="6" t="s">
@@ -14870,7 +14869,7 @@
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A293" s="26" t="s">
+      <c r="A293" s="25" t="s">
         <v>821</v>
       </c>
       <c r="B293" s="6" t="s">
@@ -14881,7 +14880,7 @@
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A294" s="26" t="s">
+      <c r="A294" s="25" t="s">
         <v>825</v>
       </c>
       <c r="B294" s="6" t="s">
@@ -14892,7 +14891,7 @@
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A295" s="26" t="s">
+      <c r="A295" s="25" t="s">
         <v>829</v>
       </c>
       <c r="B295" s="6" t="s">
@@ -14903,7 +14902,7 @@
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A296" s="26" t="s">
+      <c r="A296" s="25" t="s">
         <v>546</v>
       </c>
       <c r="B296" s="6" t="s">
@@ -14914,7 +14913,7 @@
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A297" s="26" t="s">
+      <c r="A297" s="25" t="s">
         <v>1144</v>
       </c>
       <c r="B297" s="6" t="s">
@@ -14925,7 +14924,7 @@
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A298" s="26" t="s">
+      <c r="A298" s="25" t="s">
         <v>414</v>
       </c>
       <c r="B298" s="6" t="s">
@@ -14936,7 +14935,7 @@
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A299" s="26" t="s">
+      <c r="A299" s="25" t="s">
         <v>758</v>
       </c>
       <c r="B299" s="6" t="s">
@@ -14947,7 +14946,7 @@
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A300" s="26" t="s">
+      <c r="A300" s="25" t="s">
         <v>99</v>
       </c>
       <c r="B300" s="6" t="s">
@@ -14958,7 +14957,7 @@
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A301" s="26" t="s">
+      <c r="A301" s="25" t="s">
         <v>149</v>
       </c>
       <c r="B301" s="6" t="s">
@@ -14969,7 +14968,7 @@
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A302" s="26" t="s">
+      <c r="A302" s="25" t="s">
         <v>64</v>
       </c>
       <c r="B302" s="6" t="s">
@@ -14980,7 +14979,7 @@
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A303" s="26" t="s">
+      <c r="A303" s="25" t="s">
         <v>369</v>
       </c>
       <c r="B303" s="6" t="s">
@@ -14991,7 +14990,7 @@
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A304" s="26" t="s">
+      <c r="A304" s="25" t="s">
         <v>173</v>
       </c>
       <c r="B304" s="6" t="s">
@@ -15002,7 +15001,7 @@
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A305" s="26" t="s">
+      <c r="A305" s="25" t="s">
         <v>365</v>
       </c>
       <c r="B305" s="6" t="s">
@@ -15013,7 +15012,7 @@
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A306" s="26" t="s">
+      <c r="A306" s="25" t="s">
         <v>647</v>
       </c>
       <c r="B306" s="6" t="s">
@@ -15024,7 +15023,7 @@
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A307" s="26" t="s">
+      <c r="A307" s="25" t="s">
         <v>648</v>
       </c>
       <c r="B307" s="6" t="s">
@@ -15035,7 +15034,7 @@
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A308" s="26" t="s">
+      <c r="A308" s="25" t="s">
         <v>7</v>
       </c>
       <c r="B308" s="6" t="s">
@@ -15046,7 +15045,7 @@
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A309" s="26" t="s">
+      <c r="A309" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B309" s="6" t="s">
@@ -15057,7 +15056,7 @@
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A310" s="26" t="s">
+      <c r="A310" s="25" t="s">
         <v>14</v>
       </c>
       <c r="B310" s="6" t="s">
@@ -15068,7 +15067,7 @@
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A311" s="26" t="s">
+      <c r="A311" s="25" t="s">
         <v>574</v>
       </c>
       <c r="B311" s="6" t="s">
@@ -15079,7 +15078,7 @@
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A312" s="26" t="s">
+      <c r="A312" s="25" t="s">
         <v>393</v>
       </c>
       <c r="B312" s="6" t="s">
@@ -15090,7 +15089,7 @@
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A313" s="26" t="s">
+      <c r="A313" s="25" t="s">
         <v>1145</v>
       </c>
       <c r="B313" s="6" t="s">
@@ -15101,7 +15100,7 @@
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A314" s="26" t="s">
+      <c r="A314" s="25" t="s">
         <v>247</v>
       </c>
       <c r="B314" s="6" t="s">
@@ -15112,7 +15111,7 @@
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A315" s="26" t="s">
+      <c r="A315" s="25" t="s">
         <v>622</v>
       </c>
       <c r="B315" s="6" t="s">
@@ -15123,7 +15122,7 @@
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A316" s="26" t="s">
+      <c r="A316" s="25" t="s">
         <v>260</v>
       </c>
       <c r="B316" s="6" t="s">
@@ -15134,7 +15133,7 @@
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A317" s="26" t="s">
+      <c r="A317" s="25" t="s">
         <v>16</v>
       </c>
       <c r="B317" s="6" t="s">
@@ -15145,7 +15144,7 @@
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A318" s="26" t="s">
+      <c r="A318" s="25" t="s">
         <v>522</v>
       </c>
       <c r="B318" s="6" t="s">
@@ -15156,7 +15155,7 @@
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A319" s="26" t="s">
+      <c r="A319" s="25" t="s">
         <v>182</v>
       </c>
       <c r="B319" s="6" t="s">
@@ -15167,7 +15166,7 @@
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A320" s="26" t="s">
+      <c r="A320" s="25" t="s">
         <v>465</v>
       </c>
       <c r="B320" s="6" t="s">
@@ -15178,7 +15177,7 @@
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A321" s="26" t="s">
+      <c r="A321" s="25" t="s">
         <v>466</v>
       </c>
       <c r="B321" s="6" t="s">
@@ -15189,7 +15188,7 @@
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A322" s="26" t="s">
+      <c r="A322" s="25" t="s">
         <v>572</v>
       </c>
       <c r="B322" s="6" t="s">
@@ -15200,7 +15199,7 @@
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A323" s="26" t="s">
+      <c r="A323" s="25" t="s">
         <v>692</v>
       </c>
       <c r="B323" s="6" t="s">
@@ -15211,7 +15210,7 @@
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A324" s="26" t="s">
+      <c r="A324" s="25" t="s">
         <v>470</v>
       </c>
       <c r="B324" s="6" t="s">
@@ -15222,7 +15221,7 @@
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A325" s="26" t="s">
+      <c r="A325" s="25" t="s">
         <v>850</v>
       </c>
       <c r="B325" s="6" t="s">
@@ -15233,7 +15232,7 @@
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A326" s="26" t="s">
+      <c r="A326" s="25" t="s">
         <v>433</v>
       </c>
       <c r="B326" s="6" t="s">
@@ -15244,7 +15243,7 @@
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A327" s="26" t="s">
+      <c r="A327" s="25" t="s">
         <v>439</v>
       </c>
       <c r="B327" s="6" t="s">
@@ -15255,7 +15254,7 @@
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A328" s="26" t="s">
+      <c r="A328" s="25" t="s">
         <v>448</v>
       </c>
       <c r="B328" s="6" t="s">
@@ -15266,7 +15265,7 @@
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A329" s="26" t="s">
+      <c r="A329" s="25" t="s">
         <v>450</v>
       </c>
       <c r="B329" s="6" t="s">
@@ -15277,7 +15276,7 @@
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A330" s="26" t="s">
+      <c r="A330" s="25" t="s">
         <v>877</v>
       </c>
       <c r="B330" s="6" t="s">
@@ -15288,7 +15287,7 @@
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A331" s="26" t="s">
+      <c r="A331" s="25" t="s">
         <v>883</v>
       </c>
       <c r="B331" s="6" t="s">
@@ -15299,7 +15298,7 @@
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A332" s="26" t="s">
+      <c r="A332" s="25" t="s">
         <v>885</v>
       </c>
       <c r="B332" s="6" t="s">
@@ -15310,7 +15309,7 @@
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A333" s="26" t="s">
+      <c r="A333" s="25" t="s">
         <v>887</v>
       </c>
       <c r="B333" s="6" t="s">
@@ -15321,7 +15320,7 @@
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A334" s="26" t="s">
+      <c r="A334" s="25" t="s">
         <v>888</v>
       </c>
       <c r="B334" s="6" t="s">
@@ -15332,7 +15331,7 @@
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A335" s="26" t="s">
+      <c r="A335" s="25" t="s">
         <v>890</v>
       </c>
       <c r="B335" s="6" t="s">
@@ -15343,7 +15342,7 @@
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A336" s="26" t="s">
+      <c r="A336" s="25" t="s">
         <v>892</v>
       </c>
       <c r="B336" s="6" t="s">
@@ -15354,7 +15353,7 @@
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A337" s="26" t="s">
+      <c r="A337" s="25" t="s">
         <v>673</v>
       </c>
       <c r="B337" s="6" t="s">
@@ -15365,7 +15364,7 @@
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A338" s="26" t="s">
+      <c r="A338" s="25" t="s">
         <v>667</v>
       </c>
       <c r="B338" s="6" t="s">
@@ -15376,7 +15375,7 @@
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A339" s="26" t="s">
+      <c r="A339" s="25" t="s">
         <v>902</v>
       </c>
       <c r="B339" s="6" t="s">
@@ -15387,7 +15386,7 @@
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A340" s="26" t="s">
+      <c r="A340" s="25" t="s">
         <v>597</v>
       </c>
       <c r="B340" s="6" t="s">
@@ -15398,7 +15397,7 @@
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A341" s="26" t="s">
+      <c r="A341" s="25" t="s">
         <v>941</v>
       </c>
       <c r="B341" s="6" t="s">
@@ -15409,7 +15408,7 @@
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A342" s="26" t="s">
+      <c r="A342" s="25" t="s">
         <v>814</v>
       </c>
       <c r="B342" s="6" t="s">
@@ -15420,7 +15419,7 @@
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A343" s="26" t="s">
+      <c r="A343" s="25" t="s">
         <v>944</v>
       </c>
       <c r="B343" s="6" t="s">
@@ -15431,7 +15430,7 @@
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A344" s="26" t="s">
+      <c r="A344" s="25" t="s">
         <v>947</v>
       </c>
       <c r="B344" s="6" t="s">
@@ -15442,7 +15441,7 @@
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A345" s="26" t="s">
+      <c r="A345" s="25" t="s">
         <v>960</v>
       </c>
       <c r="B345" s="6" t="s">
@@ -15453,7 +15452,7 @@
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A346" s="26" t="s">
+      <c r="A346" s="25" t="s">
         <v>963</v>
       </c>
       <c r="B346" s="6" t="s">
@@ -15464,7 +15463,7 @@
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A347" s="26" t="s">
+      <c r="A347" s="25" t="s">
         <v>965</v>
       </c>
       <c r="B347" s="6" t="s">
@@ -15475,7 +15474,7 @@
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A348" s="26" t="s">
+      <c r="A348" s="25" t="s">
         <v>969</v>
       </c>
       <c r="B348" s="6" t="s">
@@ -15486,7 +15485,7 @@
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A349" s="26" t="s">
+      <c r="A349" s="25" t="s">
         <v>974</v>
       </c>
       <c r="B349" s="6" t="s">
@@ -15497,7 +15496,7 @@
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A350" s="26" t="s">
+      <c r="A350" s="25" t="s">
         <v>978</v>
       </c>
       <c r="B350" s="6" t="s">
@@ -15508,7 +15507,7 @@
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A351" s="26" t="s">
+      <c r="A351" s="25" t="s">
         <v>628</v>
       </c>
       <c r="B351" s="6" t="s">
@@ -15519,7 +15518,7 @@
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A352" s="26" t="s">
+      <c r="A352" s="25" t="s">
         <v>994</v>
       </c>
       <c r="B352" s="6" t="s">
@@ -15530,7 +15529,7 @@
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A353" s="26" t="s">
+      <c r="A353" s="25" t="s">
         <v>861</v>
       </c>
       <c r="B353" s="6" t="s">
@@ -15541,7 +15540,7 @@
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A354" s="26" t="s">
+      <c r="A354" s="25" t="s">
         <v>999</v>
       </c>
       <c r="B354" s="6" t="s">
@@ -15552,7 +15551,7 @@
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A355" s="26" t="s">
+      <c r="A355" s="25" t="s">
         <v>866</v>
       </c>
       <c r="B355" s="6" t="s">
@@ -15563,7 +15562,7 @@
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A356" s="26" t="s">
+      <c r="A356" s="25" t="s">
         <v>281</v>
       </c>
       <c r="B356" s="6" t="s">
@@ -15574,7 +15573,7 @@
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A357" s="26" t="s">
+      <c r="A357" s="25" t="s">
         <v>1017</v>
       </c>
       <c r="B357" s="6" t="s">
@@ -15585,7 +15584,7 @@
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A358" s="26" t="s">
+      <c r="A358" s="25" t="s">
         <v>1020</v>
       </c>
       <c r="B358" s="6" t="s">
@@ -15596,7 +15595,7 @@
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A359" s="26" t="s">
+      <c r="A359" s="25" t="s">
         <v>1035</v>
       </c>
       <c r="B359" s="6" t="s">
@@ -15607,7 +15606,7 @@
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A360" s="26" t="s">
+      <c r="A360" s="25" t="s">
         <v>1038</v>
       </c>
       <c r="B360" s="6" t="s">
@@ -15618,7 +15617,7 @@
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A361" s="26" t="s">
+      <c r="A361" s="25" t="s">
         <v>870</v>
       </c>
       <c r="B361" s="6" t="s">
@@ -15629,7 +15628,7 @@
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A362" s="26" t="s">
+      <c r="A362" s="25" t="s">
         <v>1049</v>
       </c>
       <c r="B362" s="6" t="s">
@@ -15640,7 +15639,7 @@
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A363" s="26" t="s">
+      <c r="A363" s="25" t="s">
         <v>844</v>
       </c>
       <c r="B363" s="6" t="s">
@@ -15651,7 +15650,7 @@
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A364" s="26" t="s">
+      <c r="A364" s="25" t="s">
         <v>899</v>
       </c>
       <c r="B364" s="6" t="s">
@@ -15662,7 +15661,7 @@
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A365" s="26" t="s">
+      <c r="A365" s="25" t="s">
         <v>907</v>
       </c>
       <c r="B365" s="6" t="s">
@@ -15673,7 +15672,7 @@
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A366" s="26" t="s">
+      <c r="A366" s="25" t="s">
         <v>910</v>
       </c>
       <c r="B366" s="6" t="s">
@@ -15684,7 +15683,7 @@
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A367" s="26" t="s">
+      <c r="A367" s="25" t="s">
         <v>913</v>
       </c>
       <c r="B367" s="6" t="s">
@@ -15695,7 +15694,7 @@
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A368" s="26" t="s">
+      <c r="A368" s="25" t="s">
         <v>921</v>
       </c>
       <c r="B368" s="6" t="s">
@@ -15706,7 +15705,7 @@
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A369" s="26" t="s">
+      <c r="A369" s="25" t="s">
         <v>923</v>
       </c>
       <c r="B369" s="6" t="s">
@@ -15717,7 +15716,7 @@
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A370" s="26" t="s">
+      <c r="A370" s="25" t="s">
         <v>925</v>
       </c>
       <c r="B370" s="6" t="s">
@@ -15728,7 +15727,7 @@
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A371" s="26" t="s">
+      <c r="A371" s="25" t="s">
         <v>927</v>
       </c>
       <c r="B371" s="6" t="s">
@@ -15739,7 +15738,7 @@
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A372" s="26" t="s">
+      <c r="A372" s="25" t="s">
         <v>932</v>
       </c>
       <c r="B372" s="6" t="s">
@@ -15750,7 +15749,7 @@
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A373" s="26" t="s">
+      <c r="A373" s="25" t="s">
         <v>1087</v>
       </c>
       <c r="B373" s="6" t="s">
@@ -15761,7 +15760,7 @@
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A374" s="26" t="s">
+      <c r="A374" s="25" t="s">
         <v>936</v>
       </c>
       <c r="B374" s="6" t="s">
@@ -15772,7 +15771,7 @@
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A375" s="26" t="s">
+      <c r="A375" s="25" t="s">
         <v>813</v>
       </c>
       <c r="B375" s="6" t="s">
@@ -15783,7 +15782,7 @@
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A376" s="26" t="s">
+      <c r="A376" s="25" t="s">
         <v>811</v>
       </c>
       <c r="B376" s="6" t="s">
@@ -15794,7 +15793,7 @@
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A377" s="26" t="s">
+      <c r="A377" s="25" t="s">
         <v>946</v>
       </c>
       <c r="B377" s="6" t="s">
@@ -15805,7 +15804,7 @@
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A378" s="26" t="s">
+      <c r="A378" s="25" t="s">
         <v>812</v>
       </c>
       <c r="B378" s="6" t="s">
@@ -15816,7 +15815,7 @@
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A379" s="26" t="s">
+      <c r="A379" s="25" t="s">
         <v>1169</v>
       </c>
       <c r="B379" s="6" t="s">
@@ -15827,7 +15826,7 @@
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A380" s="26" t="s">
+      <c r="A380" s="25" t="s">
         <v>857</v>
       </c>
       <c r="B380" s="6" t="s">
@@ -15838,7 +15837,7 @@
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A381" s="26" t="s">
+      <c r="A381" s="25" t="s">
         <v>867</v>
       </c>
       <c r="B381" s="6" t="s">
@@ -15849,7 +15848,7 @@
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A382" s="26" t="s">
+      <c r="A382" s="25" t="s">
         <v>822</v>
       </c>
       <c r="B382" s="6" t="s">
@@ -15860,7 +15859,7 @@
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A383" s="26" t="s">
+      <c r="A383" s="25" t="s">
         <v>437</v>
       </c>
       <c r="B383" s="6" t="s">
@@ -15871,7 +15870,7 @@
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A384" s="26" t="s">
+      <c r="A384" s="25" t="s">
         <v>1091</v>
       </c>
       <c r="B384" s="6" t="s">
@@ -15882,7 +15881,7 @@
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A385" s="26" t="s">
+      <c r="A385" s="25" t="s">
         <v>1007</v>
       </c>
       <c r="B385" s="6" t="s">
@@ -15893,7 +15892,7 @@
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A386" s="26" t="s">
+      <c r="A386" s="25" t="s">
         <v>474</v>
       </c>
       <c r="B386" s="6" t="s">
@@ -15904,7 +15903,7 @@
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A387" s="26" t="s">
+      <c r="A387" s="25" t="s">
         <v>699</v>
       </c>
       <c r="B387" s="6" t="s">
@@ -15915,7 +15914,7 @@
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A388" s="26" t="s">
+      <c r="A388" s="25" t="s">
         <v>669</v>
       </c>
       <c r="B388" s="6" t="s">
@@ -15926,7 +15925,7 @@
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A389" s="26" t="s">
+      <c r="A389" s="25" t="s">
         <v>1174</v>
       </c>
       <c r="B389" s="6" t="s">
@@ -28234,7 +28233,7 @@
       <c r="A7" t="s">
         <v>1338</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" t="s">
         <v>1679</v>
       </c>
     </row>
